--- a/HW3/result/HW_3.xlsx
+++ b/HW3/result/HW_3.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28429"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Nuna\Documents\GitHub\DADS7102\class_excel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\T00229\Documents\GitHub\DADS7102\HW3\result\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{FA08DD8E-1418-4837-B209-674233AA35AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A9FA254A-269E-4E1E-9B62-4236DC270544}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{714ADFB4-38C5-4012-80EC-D1F36FD4F9FE}"/>
+    <workbookView xWindow="2715" yWindow="1965" windowWidth="21600" windowHeight="11295" xr2:uid="{714ADFB4-38C5-4012-80EC-D1F36FD4F9FE}"/>
   </bookViews>
   <sheets>
     <sheet name="HW3" sheetId="1" r:id="rId1"/>
@@ -39,10 +39,10 @@
     <definedName name="solver_eng" localSheetId="0" hidden="1">2</definedName>
     <definedName name="solver_est" localSheetId="0" hidden="1">1</definedName>
     <definedName name="solver_itr" localSheetId="0" hidden="1">2147483647</definedName>
-    <definedName name="solver_lhs1" localSheetId="0" hidden="1">'HW3'!$L$14:$L$17</definedName>
-    <definedName name="solver_lhs2" localSheetId="0" hidden="1">'HW3'!$L$5</definedName>
-    <definedName name="solver_lhs3" localSheetId="0" hidden="1">'HW3'!$E$5:$E$6</definedName>
-    <definedName name="solver_lhs4" localSheetId="0" hidden="1">'HW3'!$L$9:$L$10</definedName>
+    <definedName name="solver_lhs1" localSheetId="0" hidden="1">'HW3'!$L$9:$L$10</definedName>
+    <definedName name="solver_lhs2" localSheetId="0" hidden="1">'HW3'!$E$5:$E$6</definedName>
+    <definedName name="solver_lhs3" localSheetId="0" hidden="1">'HW3'!$L$14:$L$17</definedName>
+    <definedName name="solver_lhs4" localSheetId="0" hidden="1">'HW3'!$L$5</definedName>
     <definedName name="solver_mip" localSheetId="0" hidden="1">2147483647</definedName>
     <definedName name="solver_mni" localSheetId="0" hidden="1">30</definedName>
     <definedName name="solver_mrt" localSheetId="0" hidden="1">0.075</definedName>
@@ -54,14 +54,14 @@
     <definedName name="solver_opt" localSheetId="0" hidden="1">'HW3'!$B$17</definedName>
     <definedName name="solver_pre" localSheetId="0" hidden="1">0.000001</definedName>
     <definedName name="solver_rbv" localSheetId="0" hidden="1">2</definedName>
-    <definedName name="solver_rel1" localSheetId="0" hidden="1">3</definedName>
-    <definedName name="solver_rel2" localSheetId="0" hidden="1">2</definedName>
-    <definedName name="solver_rel3" localSheetId="0" hidden="1">1</definedName>
+    <definedName name="solver_rel1" localSheetId="0" hidden="1">2</definedName>
+    <definedName name="solver_rel2" localSheetId="0" hidden="1">1</definedName>
+    <definedName name="solver_rel3" localSheetId="0" hidden="1">3</definedName>
     <definedName name="solver_rel4" localSheetId="0" hidden="1">2</definedName>
-    <definedName name="solver_rhs1" localSheetId="0" hidden="1">'HW3'!$N$14:$N$17</definedName>
-    <definedName name="solver_rhs2" localSheetId="0" hidden="1">'HW3'!$N$5</definedName>
-    <definedName name="solver_rhs3" localSheetId="0" hidden="1">'HW3'!$G$5:$G$6</definedName>
-    <definedName name="solver_rhs4" localSheetId="0" hidden="1">'HW3'!$N$9:$N$10</definedName>
+    <definedName name="solver_rhs1" localSheetId="0" hidden="1">'HW3'!$N$9:$N$10</definedName>
+    <definedName name="solver_rhs2" localSheetId="0" hidden="1">'HW3'!$G$5:$G$6</definedName>
+    <definedName name="solver_rhs3" localSheetId="0" hidden="1">'HW3'!$N$14:$N$17</definedName>
+    <definedName name="solver_rhs4" localSheetId="0" hidden="1">'HW3'!$N$5</definedName>
     <definedName name="solver_rlx" localSheetId="0" hidden="1">2</definedName>
     <definedName name="solver_rsd" localSheetId="0" hidden="1">0</definedName>
     <definedName name="solver_scl" localSheetId="0" hidden="1">2</definedName>
@@ -86,6 +86,9 @@
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
       </xcalcf:calcFeatures>
+    </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
     </ext>
   </extLst>
 </workbook>
@@ -399,11 +402,8 @@
 </file>
 
 <file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-    </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="Sensitivity Report 1"/>
       <sheetName val="ProductMix"/>
